--- a/output/01_共通_基本コラム部品.xlsx
+++ b/output/01_共通_基本コラム部品.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="表紙・凡例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="部品画像一覧" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="差込データ" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="共通項目定義" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="部品マスタ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="レイアウト一覧" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="デザインルール" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="使い分けガイド" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表紙・凡例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部品画像一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="差込データ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="共通項目定義" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部品マスタ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="レイアウト一覧" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="デザインルール" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い分けガイド" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'差込データ'!$A$1:$L$7</definedName>
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>2</col>
@@ -342,13 +342,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -367,13 +367,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -392,13 +392,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -417,13 +417,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -442,13 +442,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -467,13 +467,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
